--- a/Result/profitability/1416.xlsx
+++ b/Result/profitability/1416.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.16</v>
       </c>
       <c r="M2" t="n">
-        <v>0.15</v>
+        <v>0.1775</v>
       </c>
       <c r="N2" t="n">
-        <v>35.3275</v>
+        <v>36.26375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.12125</v>
+        <v>0.16</v>
       </c>
       <c r="N3" t="n">
-        <v>33.7475</v>
+        <v>34.89624999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.18</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08125</v>
+        <v>0.1225</v>
       </c>
       <c r="N4" t="n">
-        <v>33.91125</v>
+        <v>35.29125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1020,10 +1020,10 @@
         <v>-0.12</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05125</v>
+        <v>0.09125000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>33.21375</v>
+        <v>34.595</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>-0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03125</v>
+        <v>0.03875000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>33.74625</v>
+        <v>35.065</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1266,10 +1266,10 @@
         <v>-0.06</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.025</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>19.54</v>
+        <v>19.68</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>-0.01</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0475</v>
+        <v>-0.01374999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>24.94125</v>
+        <v>26.10125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1522,7 +1522,7 @@
         <v>0.2</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.04500000000000001</v>
+        <v>-0.04499999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>23.775</v>
@@ -1649,7 +1649,7 @@
         <v>-0.06</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0325</v>
+        <v>-0.03249999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>21.44375</v>
@@ -9804,6 +9804,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1416</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>121</v>
+      </c>
+      <c r="D75" t="n">
+        <v>67</v>
+      </c>
+      <c r="E75" t="n">
+        <v>53</v>
+      </c>
+      <c r="F75" t="n">
+        <v>44.24</v>
+      </c>
+      <c r="G75" t="n">
+        <v>10</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.39%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>78</v>
+      </c>
+      <c r="J75" t="n">
+        <v>88</v>
+      </c>
+      <c r="K75" t="n">
+        <v>83</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.22625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>36.775</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>9.280000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2654462242562929</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.461538461538462</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3329316059053933</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
